--- a/outputs/302-1.xlsx
+++ b/outputs/302-1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="9">
   <si>
     <t xml:space="preserve">S.N</t>
   </si>
@@ -154,20 +154,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,72 +427,72 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -511,79 +515,72 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <f aca="false">ITEMS!B2</f>
-        <v>TR 200M45MM LK H K/L</v>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="str">
-        <f aca="false">ITEMS!B3</f>
-        <v>TTR 12200S45 MN 123</v>
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="str">
-        <f aca="false">ITEMS!B4</f>
-        <v>TR 1425/148V MN 123H K/L</v>
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <f aca="false">ITEMS!B5</f>
-        <v>TR 200M45 MM 123H K/L SS</v>
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <f aca="false">ITEMS!B6</f>
-        <v>TR 2.5M100* 123H K/L</v>
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <f aca="false">ITEMS!B7</f>
-        <v>TR 2.5M100**123H K/L</v>
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="str">
-        <f aca="false">ITEMS!B8</f>
-        <v>CTR 12-200M45 MM 123H K/L</v>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -605,69 +602,63 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <f aca="false">ITEMS!B2</f>
-        <v>TR 200M45MM LK H K/L</v>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="str">
-        <f aca="false">ITEMS!B3</f>
-        <v>TTR 12200S45 MN 123</v>
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="str">
-        <f aca="false">ITEMS!B4</f>
-        <v>TR 1425/148V MN 123H K/L</v>
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <f aca="false">ITEMS!B5</f>
-        <v>TR 200M45 MM 123H K/L SS</v>
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <f aca="false">ITEMS!B6</f>
-        <v>TR 2.5M100* 123H K/L</v>
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <f aca="false">ITEMS!B7</f>
-        <v>TR 2.5M100**123H K/L</v>
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -689,71 +680,71 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -776,62 +767,62 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
